--- a/artfynd/A 25943-2023 artfynd.xlsx
+++ b/artfynd/A 25943-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25943-2023 artfynd.xlsx
+++ b/artfynd/A 25943-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63206632</v>
+        <v>63206631</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667345.3351640543</v>
+        <v>667345</v>
       </c>
       <c r="R2" t="n">
-        <v>6645377.652843287</v>
+        <v>6645378</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2001-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>63206631</v>
+        <v>63206632</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667345.3351640543</v>
+        <v>667345</v>
       </c>
       <c r="R3" t="n">
-        <v>6645377.652843287</v>
+        <v>6645378</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,19 +845,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2001-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -912,12 +882,7 @@
         <v>113408822</v>
       </c>
       <c r="B4" t="n">
-        <v>57271</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
